--- a/output/pdf_financials_xlsx/ALC.xlsx
+++ b/output/pdf_financials_xlsx/ALC.xlsx
@@ -1071,46 +1071,46 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.407</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>6.495</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>1.142</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>1.205</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>13.752</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>1.167</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.238</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.081</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>1.736</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>2.855</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>2.565</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>0</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
@@ -2076,46 +2076,46 @@
         <v>82.529</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>62.577</v>
+        <v>62.17</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>26.399</v>
+        <v>19.904</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>44.065</v>
+        <v>43.745</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>25.771</v>
+        <v>24.501</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>40.505</v>
+        <v>39.363</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>45.276</v>
+        <v>44.071</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>42.393</v>
+        <v>28.641</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>19.05</v>
+        <v>17.883</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>36.347</v>
+        <v>36.109</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>70.358</v>
+        <v>70.277</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>103.049</v>
+        <v>101.313</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>71.51000000000001</v>
+        <v>68.655</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>88.752</v>
+        <v>86.187</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>135.408</v>
+        <v>134.748</v>
       </c>
     </row>
     <row r="28">
@@ -2198,46 +2198,46 @@
         <v>82.529</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>62.577</v>
+        <v>62.17</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>26.399</v>
+        <v>19.904</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>44.065</v>
+        <v>43.745</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>25.771</v>
+        <v>24.501</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>40.505</v>
+        <v>39.363</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-6.295</v>
+        <v>-7.5</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-13.321</v>
+        <v>-27.073</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-50.965</v>
+        <v>-52.132</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-38.807</v>
+        <v>-39.045</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>2.506</v>
+        <v>2.425</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>37.62</v>
+        <v>35.884</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>5.461</v>
+        <v>2.606</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>17.395</v>
+        <v>14.83</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>49.479</v>
+        <v>48.819</v>
       </c>
     </row>
     <row r="30">
@@ -2259,46 +2259,46 @@
         <v>14.16344883214059</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>11.85460083997795</v>
+        <v>11.77749866918243</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>5.371119778473608</v>
+        <v>4.049652186474438</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8.748558120881587</v>
+        <v>8.685026097763872</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>6.232511795846604</v>
+        <v>5.925372376315923</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.34858944420883</v>
+        <v>10.05682079477576</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1.389787326111002</v>
+        <v>-1.655822866693013</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-2.621206963386534</v>
+        <v>-5.327222890155666</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-8.97416482951464</v>
+        <v>-9.17965585975193</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-7.111937836748158</v>
+        <v>-7.155554741047538</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>0.4184526602468303</v>
+        <v>0.4049272550273597</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>5.549147272185526</v>
+        <v>5.293078168928905</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>0.7571892071767283</v>
+        <v>0.3613321871273675</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>2.472833658400669</v>
+        <v>2.108199089053286</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>6.501361266450827</v>
+        <v>6.414639658579658</v>
       </c>
     </row>
     <row r="31">
@@ -2462,37 +2462,37 @@
         <v>256.896</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>210.562</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>130.039</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>68.86</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>25.539</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>18.865</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>103.91</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>108.942</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>141.968</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>32.831</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>3.545</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>37.158</v>
       </c>
     </row>
     <row r="35">
@@ -2592,37 +2592,37 @@
         <v>256.896</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>210.562</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>130.039</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>68.86</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>25.539</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>18.865</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>103.91</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>108.942</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>141.968</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>32.831</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>3.545</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>37.158</v>
       </c>
     </row>
     <row r="37">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -62684,7 +62684,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -62784,7 +62784,7 @@
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
@@ -64402,7 +64402,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -65424,7 +65424,7 @@
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E540" t="inlineStr">
@@ -70798,7 +70798,7 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
@@ -70906,7 +70906,7 @@
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
@@ -73630,7 +73630,7 @@
       </c>
       <c r="D619" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E619" t="inlineStr">
@@ -76036,7 +76036,7 @@
       </c>
       <c r="D642" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E642" t="inlineStr">
@@ -78320,7 +78320,7 @@
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
@@ -78428,7 +78428,7 @@
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
@@ -80210,7 +80210,7 @@
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
@@ -80318,7 +80318,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">

--- a/output/pdf_financials_xlsx/ALC.xlsx
+++ b/output/pdf_financials_xlsx/ALC.xlsx
@@ -2131,28 +2131,28 @@
         <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>39.747</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>47.148</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>231.395</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>222.901</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>218.988</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>44.907</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>46.903</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>-51.571</v>
+        <v>45.431</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>-55.714</v>
@@ -2192,28 +2192,28 @@
         <v>38.459</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>22.184</v>
+        <v>61.931</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>82.529</v>
+        <v>129.677</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>62.17</v>
+        <v>293.565</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.904</v>
+        <v>242.805</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>43.745</v>
+        <v>262.733</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>24.501</v>
+        <v>69.408</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>39.363</v>
+        <v>86.26600000000001</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.5</v>
+        <v>89.502</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-27.073</v>
@@ -2253,28 +2253,28 @@
         <v>7.393871347907418</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>5.634718645066574</v>
+        <v>15.73042555028931</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14.16344883214059</v>
+        <v>22.2548868180336</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>11.77749866918243</v>
+        <v>55.61301908989128</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>4.049652186474438</v>
+        <v>49.40091434570569</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>8.685026097763872</v>
+        <v>52.1623719680831</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>5.925372376315923</v>
+        <v>16.78577388250829</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>10.05682079477576</v>
+        <v>22.04003004552817</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-1.655822866693013</v>
+        <v>19.75992776196773</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>-5.327222890155666</v>
@@ -6899,22 +6899,22 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>231.395</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>222.901</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>218.988</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>44.907</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>46.903</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>51.571</v>
+        <v>45.431</v>
       </c>
       <c r="L100" s="3" t="n">
         <v>55.714</v>
@@ -49054,7 +49054,11 @@
           <t>Depreciation of property, plant, and equipment 33</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E382" t="inlineStr">
         <is>
           <t>-</t>
@@ -50836,7 +50840,11 @@
           <t>Depreciation of property, plant, and equipment 15</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E399" t="inlineStr">
         <is>
           <t>-</t>
@@ -52812,7 +52820,11 @@
           <t>Depreciation of property, plant, and equipment total</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E418" t="inlineStr">
         <is>
           <t>-</t>
@@ -55502,7 +55514,11 @@
           <t>Depreciation of property, plant and equipment total</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
           <t>-</t>
@@ -73312,7 +73328,11 @@
           <t>Depreciation of property, plant, and equipment 33</t>
         </is>
       </c>
-      <c r="D616" t="inlineStr"/>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E616" t="inlineStr">
         <is>
           <t>-</t>
@@ -73354,10 +73374,10 @@
         </is>
       </c>
       <c r="M616" s="5" t="n">
-        <v>-46.903</v>
+        <v>46.903</v>
       </c>
       <c r="N616" s="5" t="n">
-        <v>-45.431</v>
+        <v>45.431</v>
       </c>
       <c r="O616" t="inlineStr">
         <is>
@@ -75722,7 +75742,11 @@
           <t>Depreciation of property, plant, and equipment 15</t>
         </is>
       </c>
-      <c r="D639" t="inlineStr"/>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E639" t="inlineStr">
         <is>
           <t>-</t>
@@ -75759,10 +75783,10 @@
         </is>
       </c>
       <c r="L639" s="5" t="n">
-        <v>-44.907</v>
+        <v>44.907</v>
       </c>
       <c r="M639" s="5" t="n">
-        <v>-46.903</v>
+        <v>46.903</v>
       </c>
       <c r="N639" t="inlineStr">
         <is>
@@ -83694,7 +83718,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D715" t="inlineStr"/>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E715" t="inlineStr">
         <is>
           <t>-</t>
@@ -83706,10 +83734,10 @@
         </is>
       </c>
       <c r="G715" s="5" t="n">
-        <v>-39.747</v>
+        <v>39.747</v>
       </c>
       <c r="H715" s="5" t="n">
-        <v>-47.148</v>
+        <v>47.148</v>
       </c>
       <c r="I715" t="inlineStr">
         <is>
